--- a/artfynd/A 51873-2023 artfynd.xlsx
+++ b/artfynd/A 51873-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51873-2023 artfynd.xlsx
+++ b/artfynd/A 51873-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113240820</v>
+        <v>113240828</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538246</v>
+        <v>538082</v>
       </c>
       <c r="R2" t="n">
-        <v>7107894</v>
+        <v>7108180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113240830</v>
+        <v>113240829</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538216</v>
+        <v>538156</v>
       </c>
       <c r="R3" t="n">
-        <v>7108027</v>
+        <v>7108105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113240814</v>
+        <v>113240830</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538343</v>
+        <v>538216</v>
       </c>
       <c r="R4" t="n">
-        <v>7107925</v>
+        <v>7108027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113240812</v>
+        <v>113240820</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538363</v>
+        <v>538246</v>
       </c>
       <c r="R5" t="n">
-        <v>7107927</v>
+        <v>7107894</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113240816</v>
+        <v>113240812</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538301</v>
+        <v>538363</v>
       </c>
       <c r="R6" t="n">
-        <v>7107754</v>
+        <v>7107927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,12 +1183,7 @@
         <v>113240813</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113240829</v>
+        <v>113240814</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538156</v>
+        <v>538343</v>
       </c>
       <c r="R8" t="n">
-        <v>7108105</v>
+        <v>7107925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,12 +1387,7 @@
         <v>113240815</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113240828</v>
+        <v>113240816</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1497,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538082</v>
+        <v>538301</v>
       </c>
       <c r="R10" t="n">
-        <v>7108180</v>
+        <v>7107754</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113240817</v>
+        <v>113240831</v>
       </c>
       <c r="B11" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,50 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Havsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538268</v>
+        <v>538082</v>
       </c>
       <c r="R11" t="n">
-        <v>7107816</v>
+        <v>7108257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,11 +1661,16 @@
           <t>2023-11-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1748,6 +1687,119 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113240817</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538268</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7107816</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51873-2023 artfynd.xlsx
+++ b/artfynd/A 51873-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113240828</v>
+        <v>134758305</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538082</v>
+        <v>538454</v>
       </c>
       <c r="R2" t="n">
-        <v>7108180</v>
+        <v>7107880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,57 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113240829</v>
+        <v>134758276</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538156</v>
+        <v>538111</v>
       </c>
       <c r="R3" t="n">
-        <v>7108105</v>
+        <v>7108219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,57 +861,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113240830</v>
+        <v>134758277</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538216</v>
+        <v>538128</v>
       </c>
       <c r="R4" t="n">
-        <v>7108027</v>
+        <v>7108236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113240820</v>
+        <v>134758290</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538246</v>
+        <v>538467</v>
       </c>
       <c r="R5" t="n">
-        <v>7107894</v>
+        <v>7107906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,22 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113240812</v>
+        <v>134758292</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538363</v>
+        <v>538281</v>
       </c>
       <c r="R6" t="n">
-        <v>7107927</v>
+        <v>7108058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,17 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1164,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113240813</v>
+        <v>134758293</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538333</v>
+        <v>538425</v>
       </c>
       <c r="R7" t="n">
-        <v>7107909</v>
+        <v>7107932</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,17 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,22 +1265,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113240814</v>
+        <v>134758306</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,34 +1292,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538343</v>
+        <v>538420</v>
       </c>
       <c r="R8" t="n">
-        <v>7107925</v>
+        <v>7107936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,17 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,22 +1366,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113240815</v>
+        <v>134758320</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,34 +1393,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538138</v>
+        <v>538455</v>
       </c>
       <c r="R9" t="n">
-        <v>7108181</v>
+        <v>7107880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,17 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,22 +1467,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113240816</v>
+        <v>134758324</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1494,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538301</v>
+        <v>538379</v>
       </c>
       <c r="R10" t="n">
-        <v>7107754</v>
+        <v>7108006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,17 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,57 +1568,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113240831</v>
+        <v>134758289</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>92689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538082</v>
+        <v>538410</v>
       </c>
       <c r="R11" t="n">
-        <v>7108257</v>
+        <v>7107888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,24 +1649,19 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1678,22 +1669,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113240817</v>
+        <v>134758283</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,50 +1696,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Havsnäs, Jmt</t>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538268</v>
+        <v>538412</v>
       </c>
       <c r="R12" t="n">
-        <v>7107816</v>
+        <v>7107947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,15 +1770,3684 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134758288</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>538430</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7107889</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134758291</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>538112</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7108220</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134758311</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>538448</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7107869</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134758286</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>538419</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7107921</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134758318</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>538426</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7107904</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134758278</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>538333</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7108157</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134758284</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96410</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>538256</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7107894</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134758285</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92199</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>538438</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7107938</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134758321</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92199</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>538329</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7108059</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113240828</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>538082</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7108180</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113240829</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>538156</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7108105</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113240830</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>538216</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7108027</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134758296</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>538469</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7107884</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134758317</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>538339</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7108068</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spridda och vanlig i skogen, men inga riktigt garnlavsdraperade träd.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134758309</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>538223</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7107782</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113240820</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>538246</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7107894</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134758302</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>538250</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7107894</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134758303</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538254</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7107907</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134758312</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>538019</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7108236</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134758281</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>538318</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7108165</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134758307</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>538313</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7108173</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>113240812</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>538363</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7107927</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>113240813</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>538333</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7107909</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>113240814</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>538343</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7107925</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>113240815</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>538138</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7108181</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>113240816</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>538301</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7107754</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>113240831</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>538082</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7108257</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134758301</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>538272</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7108047</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>113240817</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Havsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>538268</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7107816</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134758315</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>538466</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7107883</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134758298</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99533</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>538427</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7107896</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rik förekomst.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134758314</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99533</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>538435</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7107883</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134758322</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>538255</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7107918</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134758297</v>
+      </c>
+      <c r="B46" t="n">
+        <v>105771</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>224074</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordlundarv</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Stellaria nemorum subsp. nemorum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>538427</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7107896</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134758319</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>538315</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7108174</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134758304</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skog sydost om Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>538422</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7107929</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51873-2023 artfynd.xlsx
+++ b/artfynd/A 51873-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758290</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758292</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758293</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758306</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758320</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758324</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758289</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758283</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758291</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758311</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758286</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758318</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758278</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758284</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758285</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240828</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240829</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2998,6 +3113,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240830</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758296</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3205,6 +3330,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758317</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3306,6 +3436,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758309</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3403,6 +3538,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240820</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3504,6 +3644,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758302</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3605,6 +3750,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758303</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3706,6 +3856,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758312</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3807,6 +3962,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758281</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3908,6 +4068,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758307</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4010,6 +4175,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240812</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4112,6 +4282,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240813</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4214,6 +4389,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240814</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4316,6 +4496,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240815</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4418,6 +4603,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240816</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4520,6 +4710,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240831</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4626,6 +4821,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758301</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4739,6 +4939,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113240817</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4840,6 +5045,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758315</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758298</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5047,6 +5262,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758314</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758322</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5245,6 +5470,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758297</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5346,6 +5576,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758319</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5448,8 +5683,62 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>